--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>22</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1504</v>
+        <v>1977</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>994</v>
+        <v>1307</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>684</v>
+        <v>903</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>314</v>
+        <v>389</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>470</v>
+        <v>617</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>412</v>
+        <v>534</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>214</v>
+        <v>280</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>240</v>
+        <v>310</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>256</v>
+        <v>337</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>5</v>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -983,47 +983,47 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>03733</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>VENEZIA</t>
+          <t>MOGLIANO VENETO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,51 +1033,51 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>MARINI EMANUELE</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>6</v>
+        <v>259</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>03733</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>MOGLIANO VENETO</t>
+          <t>VENEZIA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,193 +1087,189 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>182</v>
+        <v>8</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>120</v>
+        <v>221</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>04044</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>TRIESTE</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr"/>
+          <t>PORDENONE</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ZAMPIERI ANTONIO</t>
+          <t>FELICI FILIPPO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>04044</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>PORDENONE</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+          <t>TRIESTE</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>ZAMPIERI ANTONIO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>51141</t>
+          <t>03743</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SPINEA</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+          <t>VENEZIA</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G19" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="I19" s="12" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1284,62 +1280,66 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03743</t>
+          <t>51141</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>VENEZIA</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
+          <t>SPINEA</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>MARINI EMANUELE</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03734</t>
+          <t>56033</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>MUSILE DI PIAVE</t>
+          <t>CASTELFRANCO VENETO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1349,51 +1349,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>MARINI EMANUELE</t>
+          <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>03734</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>PIANIGA</t>
+          <t>MUSILE DI PIAVE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1403,51 +1403,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="G22" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="J22" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H22" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="K22" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>04247</t>
+          <t>03610</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>BRUGNERA</t>
+          <t>MONTEBELLUNA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1457,32 +1457,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>2</v>
@@ -1515,28 +1515,28 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -1550,12 +1550,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>03610</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>MONTEBELLUNA</t>
+          <t>PIANIGA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1565,39 +1565,39 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1619,28 +1619,28 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -1654,12 +1654,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>56033</t>
+          <t>04247</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CASTELFRANCO VENETO</t>
+          <t>BRUGNERA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1669,39 +1669,39 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>2</v>
@@ -1739,16 +1739,16 @@
         <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>4</v>
@@ -1781,73 +1781,69 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>56062</t>
+          <t>13623</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>UDINE</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+          <t>VITTORIO VENETO</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>0</v>
@@ -1856,26 +1852,26 @@
         <v>0</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>04051</t>
+          <t>56062</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>TRIESTE</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1885,20 +1881,20 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>ZAMPIERI ANTONIO</t>
+          <t>FELICI FILIPPO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>19</v>
+        <v>164</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>0</v>
@@ -1917,32 +1913,36 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>13623</t>
+          <t>04051</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>VITTORIO VENETO</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
+          <t>TRIESTE</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>ZAMPIERI ANTONIO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>
@@ -1960,14 +1960,14 @@
         <v>0</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>534</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.07677902621722846</v>
+        <v>41</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>337</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.01483679525222552</v>
+        <v>5</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>225</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.09777777777777778</v>
+        <v>22</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>176</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1420454545454546</v>
+        <v>25</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>169</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.005917159763313609</v>
+        <v>1</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>221</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.02714932126696833</v>
+        <v>6</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>192</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.03125</v>
+        <v>6</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>160</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.2125</v>
+        <v>34</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>77</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.02597402597402598</v>
+        <v>2</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>47</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.0425531914893617</v>
+        <v>2</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>104</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.25</v>
+        <v>26</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>54</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.03703703703703703</v>
+        <v>2</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>64</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.0625</v>
+        <v>4</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>22</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1977</v>
+        <v>2087</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1307</v>
+        <v>1382</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>903</v>
+        <v>967</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>617</v>
+        <v>653</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>534</v>
+        <v>568</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>41</v>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,35 +983,35 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>191</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>10</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>1</v>
@@ -1072,12 +1072,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>03733</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>VENEZIA</t>
+          <t>PORDENONE</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,51 +1087,51 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>MARINI EMANUELE</t>
+          <t>FELICI FILIPPO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F16" s="12" t="n">
+        <v>273</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>133</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>236</v>
+      </c>
+      <c r="I16" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="J16" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>210</v>
+      </c>
+      <c r="M16" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H16" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="I16" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>221</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>03733</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>PORDENONE</t>
+          <t>VENEZIA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,39 +1141,39 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>253</v>
+        <v>95</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>221</v>
+        <v>13</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>192</v>
+        <v>235</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>6</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1195,31 +1195,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>7</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>14</v>
@@ -1266,14 +1266,14 @@
         <v>10</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>2</v>
@@ -1311,16 +1311,16 @@
         <v>6</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
@@ -1365,16 +1365,16 @@
         <v>19</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -1407,19 +1407,19 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>4</v>
@@ -1428,26 +1428,26 @@
         <v>25</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>03610</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MONTEBELLUNA</t>
+          <t>PORTOGRUARO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1457,51 +1457,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J23" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K23" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K23" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="L23" s="12" t="n">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PORTOGRUARO</t>
+          <t>PIANIGA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1511,35 +1511,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>MARINI EMANUELE</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>167</v>
+        <v>57</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1550,12 +1550,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>03610</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PIANIGA</t>
+          <t>MONTEBELLUNA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1565,39 +1565,39 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="G25" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K25" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H25" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="J25" s="12" t="n">
+      <c r="L25" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="M25" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K25" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>104</v>
-      </c>
-      <c r="M25" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>4</v>
@@ -1640,7 +1640,7 @@
         <v>11</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>3</v>
@@ -1685,7 +1685,7 @@
         <v>4</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>8</v>
@@ -1694,10 +1694,10 @@
         <v>13</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>33</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>2</v>
@@ -1748,14 +1748,14 @@
         <v>6</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>4</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>1</v>
@@ -1793,7 +1793,7 @@
         <v>2</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>6</v>
@@ -1802,7 +1802,7 @@
         <v>6</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -1831,13 +1831,13 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>0</v>
@@ -1849,17 +1849,17 @@
         <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -525,7 +525,7 @@
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1188,7 +1188,11 @@
           <t>TRIESTE</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
           <t>ZAMPIERI ANTONIO</t>
@@ -1238,7 +1242,11 @@
           <t>VENEZIA</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t>MARINI EMANUELE</t>
@@ -1612,7 +1620,11 @@
           <t>UDINE</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t>FELICI FILIPPO</t>
@@ -1824,7 +1836,11 @@
           <t>VITTORIO VENETO</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
           <t>MARCHIORI GIOVANNI AGOSTINO</t>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>22</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2087</v>
+        <v>2215</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1382</v>
+        <v>1453</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>967</v>
+        <v>1036</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>413</v>
+        <v>443</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>653</v>
+        <v>675</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>568</v>
+        <v>596</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>6</v>
@@ -995,16 +995,16 @@
         <v>10</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>38</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>31</v>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>17</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>1</v>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>9</v>
@@ -1157,7 +1157,7 @@
         <v>13</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>21</v>
@@ -1166,7 +1166,7 @@
         <v>49</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>6</v>
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>3</v>
@@ -1265,23 +1265,23 @@
         <v>4</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>2</v>
@@ -1325,10 +1325,10 @@
         <v>23</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -1415,28 +1415,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -1469,28 +1469,28 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>52834</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PIANIGA</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,51 +1519,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>FELICI FILIPPO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
+        <v>161</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="J24" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H24" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="I24" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="K24" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>03610</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>MONTEBELLUNA</t>
+          <t>PIANIGA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>52834</t>
+          <t>03610</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>MONTEBELLUNA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,35 +1627,35 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>155</v>
+        <v>18</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>159</v>
+        <v>47</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>65</v>
@@ -1700,13 +1700,13 @@
         <v>29</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>3</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>19</v>
@@ -1757,17 +1757,17 @@
         <v>12</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>4</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
         <v>29</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>1</v>
@@ -1847,28 +1847,28 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>22</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2215</v>
+        <v>2329</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1453</v>
+        <v>1533</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1036</v>
+        <v>1097</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>675</v>
+        <v>702</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>596</v>
+        <v>622</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>8</v>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>192</v>
@@ -995,19 +995,19 @@
         <v>10</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>105</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>31</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>42</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="J16" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="K16" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K16" s="12" t="n">
-        <v>29</v>
-      </c>
       <c r="L16" s="12" t="n">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>49</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>6</v>
@@ -1199,35 +1199,35 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>8</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J18" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>184</v>
+      </c>
+      <c r="M18" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="K18" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L18" s="12" t="n">
-        <v>175</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>38</v>
-      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>3</v>
@@ -1265,16 +1265,16 @@
         <v>4</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>3</v>
@@ -1307,35 +1307,35 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>71</v>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>68</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>23</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -1415,28 +1415,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -1469,28 +1469,28 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
@@ -1544,14 +1544,14 @@
         <v>13</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1577,19 +1577,19 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>2</v>
@@ -1598,10 +1598,10 @@
         <v>23</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1631,28 +1631,28 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="J26" s="12" t="n">
         <v>18</v>
-      </c>
-      <c r="H26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>17</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>2</v>
@@ -1685,31 +1685,31 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>2</v>
@@ -1751,16 +1751,16 @@
         <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>4</v>
@@ -1796,7 +1796,7 @@
         <v>29</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>1</v>
@@ -1814,7 +1814,7 @@
         <v>6</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -1847,19 +1847,19 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>1</v>
@@ -1868,7 +1868,7 @@
         <v>1</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -1901,19 +1901,19 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>22</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2329</v>
+        <v>2478</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1533</v>
+        <v>1618</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1097</v>
+        <v>1143</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>462</v>
+        <v>484</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>702</v>
+        <v>732</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>622</v>
+        <v>655</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>46</v>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J12" s="12" t="n">
         <v>43</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -983,35 +983,35 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>10</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>39</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>33</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>1</v>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>70</v>
@@ -1163,10 +1163,10 @@
         <v>22</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>6</v>
@@ -1199,47 +1199,47 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>8</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>16</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>03743</t>
+          <t>51141</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>VENEZIA</t>
+          <t>SPINEA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,51 +1249,51 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>MARINI EMANUELE</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>51141</t>
+          <t>03743</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SPINEA</t>
+          <t>VENEZIA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,35 +1303,35 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>153</v>
+        <v>108</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>1</v>
@@ -1373,16 +1373,16 @@
         <v>21</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>23</v>
@@ -1433,10 +1433,10 @@
         <v>4</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -1472,13 +1472,13 @@
         <v>57</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>33</v>
@@ -1490,7 +1490,7 @@
         <v>22</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>52834</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>PIANIGA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,51 +1519,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>166</v>
+        <v>6</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I24" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>126</v>
+      </c>
+      <c r="M24" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="J24" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K24" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>173</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>52834</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PIANIGA</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,39 +1573,39 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>FELICI FILIPPO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G25" s="12" t="n">
+        <v>170</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="J25" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H25" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="K25" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>119</v>
+        <v>177</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>3</v>
@@ -1697,16 +1697,16 @@
         <v>5</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>4</v>
@@ -1742,7 +1742,7 @@
         <v>36</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>2</v>
@@ -1760,14 +1760,14 @@
         <v>7</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>4</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>67</v>
@@ -1811,10 +1811,10 @@
         <v>6</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>0</v>
@@ -1859,7 +1859,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>1</v>
@@ -1868,14 +1868,14 @@
         <v>1</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1901,28 +1901,28 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>193</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="12" t="n">
-        <v>184</v>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="12" t="n">
+      <c r="K31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="12" t="n">
         <v>5</v>
-      </c>
-      <c r="I31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -525,7 +525,7 @@
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1944,11 +1944,7 @@
           <t>TRIESTE</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
           <t>ZAMPIERI ANTONIO</t>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N32" headerRowCount="1">
-  <autoFilter ref="A10:N32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N33" headerRowCount="1">
+  <autoFilter ref="A10:N33"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,11 +520,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -673,7 +673,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>2478</v>
@@ -1983,6 +1983,60 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>14289</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SAN DANIELE DEL FRIULI</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>FELICI FILIPPO</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N33" headerRowCount="1">
-  <autoFilter ref="A10:N33"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O33" headerRowCount="1">
+  <autoFilter ref="A10:O33"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>VIA LIVIANA SCATTOLON</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>484</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>732</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>280</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>261</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>215</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>655</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>VIA VENEZIA 88</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>338</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>380</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>399</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>VIALE TREVISO 38</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>248</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>289</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>VIA VITTORIO VENETO</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>213</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>214</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>VIA CASALE SUL SILE 14</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>320</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>113</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>207</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>VIALE VENEZIA 46</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>FELICI FILIPPO</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>323</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>283</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>111</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>249</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>ROTATORIA ROMEA</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>MARINI EMANUELE</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>124</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>109</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>286</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>V.LE MIRAMARE  49 0049</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>ZAMPIERI ANTONIO</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>194</v>
       </c>
-      <c r="H18" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>195</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>COSTITUZIONE CREA</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>162</v>
       </c>
-      <c r="M19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>VIA ORLANDA 6A</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>MARINI EMANUELE</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>VIA CIRCONVALLAZIONE EST 85</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>175</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="M21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>VIALE MARCONI 48</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>MARINI EMANUELE</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="M22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>VIA PORDENONE, 78</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>MARINI EMANUELE</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>197</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>175</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="M23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>STAZIONE 1</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>VIALE MONSIGNORE GIUSEPPE NOGARA 92</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>FELICI FILIPPO</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="F25" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="H25" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="M25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="N25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>VIA BASSANESE, 58</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="F26" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H26" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>UNGARESCA 0017</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="N27" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>VIA VALENTINIS, SS 14 61</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>ZAMPIERI ANTONIO</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="L28" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="M28" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>VIA NOVENTA 150</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>MARINI EMANUELE</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="M29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>VIA S.ANTONIO DA PADOVA SS 51</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F30" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H30" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12" t="n">
         <v>13</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="M30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1892,42 +2008,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>VIALE TRICESIMO 93</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>FELICI FILIPPO</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>193</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>6</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J31" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K31" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="M31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="N31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1944,21 +2065,23 @@
           <t>TRIESTE</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>ALFONSO VALERIO 0001</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>ZAMPIERI ANTONIO</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
@@ -1977,7 +2100,10 @@
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1996,17 +2122,19 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>VIA VENEZIA SS 463 KM. 17+262 89/91</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>FELICI FILIPPO</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F33" s="12" t="n">
         <v>0</v>
       </c>
@@ -2031,7 +2159,10 @@
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="N33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2478</v>
+        <v>2589</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1618</v>
+        <v>1687</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1143</v>
+        <v>1209</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>484</v>
+        <v>501</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>732</v>
+        <v>767</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>655</v>
+        <v>696</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>240</v>
+        <v>289</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>33</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1081,10 +1081,10 @@
         <v>158</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>35</v>
@@ -1093,20 +1093,20 @@
         <v>113</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>47</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>6</v>
@@ -1255,35 +1255,35 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>16</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>0</v>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>6</v>
@@ -1571,7 +1571,7 @@
         <v>22</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1609,16 +1609,16 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>27</v>
@@ -1627,10 +1627,10 @@
         <v>3</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>36</v>
@@ -1668,19 +1668,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>6</v>
@@ -1689,14 +1689,14 @@
         <v>13</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>0</v>
@@ -1739,23 +1739,23 @@
         <v>0</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>5</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>3</v>
@@ -1798,7 +1798,7 @@
         <v>5</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>10</v>
@@ -1807,7 +1807,7 @@
         <v>17</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>4</v>
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>23</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>67</v>
@@ -1922,10 +1922,10 @@
         <v>6</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12" t="n">
         <v>14</v>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>13</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>1</v>
@@ -1984,14 +1984,14 @@
         <v>1</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K31" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M31" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="N31" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N31" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2057,42 +2057,46 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04051</t>
+          <t>14289</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>TRIESTE</t>
+          <t>SAN DANIELE DEL FRIULI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>ALFONSO VALERIO 0001</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>VIA VENEZIA, 89/91</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>ZAMPIERI ANTONIO</t>
+          <t>FELICI FILIPPO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>0</v>
@@ -2105,41 +2109,37 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>14289</t>
+          <t>04051</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SAN DANIELE DEL FRIULI</t>
+          <t>TRIESTE</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA VENEZIA SS 463 KM. 17+262 89/91</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+          <t>ALFONSO VALERIO 0001</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>ZAMPIERI ANTONIO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2589</v>
+        <v>2719</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1687</v>
+        <v>1760</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1209</v>
+        <v>1286</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>501</v>
+        <v>532</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>767</v>
+        <v>801</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>12</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>56</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>10</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>69</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>33</v>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>28</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>18</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>46</v>
@@ -1276,10 +1276,10 @@
         <v>16</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>51141</t>
+          <t>03743</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SPINEA</t>
+          <t>VENEZIA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COSTITUZIONE CREA</t>
+          <t>VIA ORLANDA 6A</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03743</t>
+          <t>51141</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>VENEZIA</t>
+          <t>SPINEA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA ORLANDA 6A</t>
+          <t>COSTITUZIONE CREA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,39 +1369,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>MARINI EMANUELE</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>69</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>24</v>
@@ -1512,7 +1512,7 @@
         <v>33</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>6</v>
@@ -1571,7 +1571,7 @@
         <v>22</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>27</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>36</v>
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>0</v>
@@ -1689,10 +1689,10 @@
         <v>13</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>0</v>
@@ -1739,16 +1739,16 @@
         <v>0</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>2</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>3</v>
@@ -1798,7 +1798,7 @@
         <v>5</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>10</v>
@@ -1807,7 +1807,7 @@
         <v>17</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>4</v>
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>8</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>1</v>
@@ -1922,13 +1922,13 @@
         <v>6</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>13623</t>
+          <t>56062</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>VITTORIO VENETO</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIA S.ANTONIO DA PADOVA SS 51</t>
+          <t>VIALE TRICESIMO 93</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,56 +1959,56 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>FELICI FILIPPO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K30" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L30" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M30" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="N30" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="N30" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>56062</t>
+          <t>13623</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>VITTORIO VENETO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIALE TRICESIMO 93</t>
+          <t>VIA S.ANTONIO DA PADOVA SS 51</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,39 +2018,39 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="G31" s="12" t="n">
-        <v>208</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I31" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="K31" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2081,22 +2081,22 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2719</v>
+        <v>2841</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1760</v>
+        <v>1857</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1286</v>
+        <v>1369</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>532</v>
+        <v>554</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>801</v>
+        <v>849</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>749</v>
+        <v>794</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>423</v>
+        <v>452</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>49</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>44</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>56</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>33</v>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>352</v>
+        <v>385</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>3</v>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>47</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>23</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>7</v>
@@ -1255,35 +1255,35 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>16</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>6</v>
@@ -1326,23 +1326,23 @@
         <v>4</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>2</v>
@@ -1385,19 +1385,19 @@
         <v>8</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>48</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>2</v>
@@ -1444,7 +1444,7 @@
         <v>26</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>5</v>
@@ -1453,7 +1453,7 @@
         <v>31</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>33</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>6</v>
@@ -1571,7 +1571,7 @@
         <v>22</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>52834</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PIANIGA</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>STAZIONE 1</t>
+          <t>VIALE MONSIGNORE GIUSEPPE NOGARA 92</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,56 +1605,56 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>FELICI FILIPPO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>6</v>
+        <v>189</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>52834</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>PIANIGA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIALE MONSIGNORE GIUSEPPE NOGARA 92</t>
+          <t>STAZIONE 1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,39 +1664,39 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>183</v>
+        <v>6</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>196</v>
+        <v>145</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>2</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>3</v>
@@ -1798,7 +1798,7 @@
         <v>5</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>10</v>
@@ -1807,14 +1807,14 @@
         <v>17</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>8</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>1</v>
@@ -1916,16 +1916,16 @@
         <v>2</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>1</v>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>0</v>
@@ -2043,14 +2043,14 @@
         <v>1</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2841</v>
+        <v>2946</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1857</v>
+        <v>1934</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1369</v>
+        <v>1432</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>849</v>
+        <v>884</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>794</v>
+        <v>832</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>60</v>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>452</v>
+        <v>477</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>9</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>49</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>44</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>12</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>19</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>23</v>
@@ -1217,14 +1217,14 @@
         <v>64</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>2</v>
@@ -1391,10 +1391,10 @@
         <v>27</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>1</v>
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>5</v>
@@ -1453,7 +1453,7 @@
         <v>31</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>33</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>6</v>
@@ -1571,7 +1571,7 @@
         <v>22</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>7</v>
@@ -1630,31 +1630,31 @@
         <v>14</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>03610</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PIANIGA</t>
+          <t>MONTEBELLUNA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>STAZIONE 1</t>
+          <t>VIA BASSANESE, 58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,56 +1664,56 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
         <v>57</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H25" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L25" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I25" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>27</v>
-      </c>
       <c r="M25" s="12" t="n">
-        <v>145</v>
+        <v>57</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03610</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MONTEBELLUNA</t>
+          <t>PIANIGA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA BASSANESE, 58</t>
+          <t>STAZIONE 1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,39 +1723,39 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>3</v>
@@ -1804,10 +1804,10 @@
         <v>10</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>4</v>
@@ -1848,13 +1848,13 @@
         <v>48</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>43</v>
@@ -1866,14 +1866,14 @@
         <v>8</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>1</v>
@@ -1916,16 +1916,16 @@
         <v>2</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>1</v>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,22 +2022,22 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>1</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2946</v>
+        <v>3079</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1934</v>
+        <v>2021</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1432</v>
+        <v>1506</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>568</v>
+        <v>590</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>884</v>
+        <v>942</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>832</v>
+        <v>878</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>9</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>49</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>488</v>
+        <v>519</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>61</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>17</v>
@@ -1031,19 +1031,19 @@
         <v>12</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>45</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>19</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>23</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>9</v>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>57</v>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>8</v>
@@ -1326,19 +1326,19 @@
         <v>4</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>27</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>1</v>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>33</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>6</v>
@@ -1571,7 +1571,7 @@
         <v>22</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1609,35 +1609,35 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1668,22 +1668,22 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>6</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>26</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>3</v>
@@ -1798,16 +1798,16 @@
         <v>5</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>4</v>
@@ -1845,19 +1845,19 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>18</v>
@@ -1866,31 +1866,31 @@
         <v>8</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>03679</t>
+          <t>56062</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SAN DONÀ DI PIAVE</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA NOVENTA 150</t>
+          <t>VIALE TRICESIMO 93</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,35 +1900,35 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>MARINI EMANUELE</t>
+          <t>FELICI FILIPPO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>56062</t>
+          <t>03679</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>SAN DONÀ DI PIAVE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIALE TRICESIMO 93</t>
+          <t>VIA NOVENTA 150</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,35 +1959,35 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>253</v>
+        <v>78</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I30" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="K30" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="J30" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="L30" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2043,14 +2043,14 @@
         <v>1</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2081,22 +2081,22 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3079</v>
+        <v>3205</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2021</v>
+        <v>2109</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1506</v>
+        <v>1573</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>590</v>
+        <v>612</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>942</v>
+        <v>975</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>878</v>
+        <v>922</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>496</v>
+        <v>527</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>9</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>45</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>102</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>46</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>36</v>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>7</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>433</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>363</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>23</v>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>19</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>8</v>
@@ -1326,23 +1326,23 @@
         <v>4</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K19" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="L19" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="L19" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="M19" s="12" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>45</v>
@@ -1391,17 +1391,17 @@
         <v>27</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>PORTOGRUARO</t>
+          <t>PIANIGA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA PORDENONE, 78</t>
+          <t>STAZIONE 1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>MARINI EMANUELE</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>254</v>
+        <v>95</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>223</v>
+        <v>26</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>9</v>
@@ -1630,31 +1630,31 @@
         <v>14</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>03610</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>MONTEBELLUNA</t>
+          <t>PORTOGRUARO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA BASSANESE, 58</t>
+          <t>VIA PORDENONE, 78</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,56 +1664,56 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>03610</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>PIANIGA</t>
+          <t>MONTEBELLUNA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>STAZIONE 1</t>
+          <t>VIA BASSANESE, 58</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,39 +1723,39 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>3</v>
@@ -1798,16 +1798,16 @@
         <v>5</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>4</v>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>04131</t>
+          <t>56062</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>MONFALCONE</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA VALENTINIS, SS 14 61</t>
+          <t>VIALE TRICESIMO 93</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,56 +1841,56 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>ZAMPIERI ANTONIO</t>
+          <t>FELICI FILIPPO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>40</v>
+        <v>285</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>8</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>56062</t>
+          <t>04131</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>MONFALCONE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIALE TRICESIMO 93</t>
+          <t>VIA VALENTINIS, SS 14 61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,39 +1900,39 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>ZAMPIERI ANTONIO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>266</v>
+        <v>43</v>
       </c>
       <c r="H29" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="K29" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="L29" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>1</v>
@@ -1975,16 +1975,16 @@
         <v>2</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>1</v>
@@ -2022,35 +2022,35 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2102,14 +2102,14 @@
         <v>0</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3205</v>
+        <v>3327</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2109</v>
+        <v>2196</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1573</v>
+        <v>1652</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>612</v>
+        <v>646</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>975</v>
+        <v>998</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>922</v>
+        <v>965</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>9</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>541</v>
+        <v>574</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>45</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>13</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>46</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>46</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>23</v>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>24</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,35 +1255,35 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>22</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>27</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>3</v>
@@ -1385,7 +1385,7 @@
         <v>10</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>27</v>
@@ -1394,10 +1394,10 @@
         <v>56</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>37</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>PIANIGA</t>
+          <t>PORTOGRUARO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>STAZIONE 1</t>
+          <t>VIA PORDENONE, 78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>95</v>
+        <v>275</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>26</v>
+        <v>246</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>52834</t>
+          <t>03610</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>MONTEBELLUNA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIALE MONSIGNORE GIUSEPPE NOGARA 92</t>
+          <t>VIA BASSANESE, 58</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,56 +1605,56 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>203</v>
+        <v>26</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>230</v>
+        <v>61</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>52834</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PORTOGRUARO</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA PORDENONE, 78</t>
+          <t>VIALE MONSIGNORE GIUSEPPE NOGARA 92</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,56 +1664,56 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>MARINI EMANUELE</t>
+          <t>FELICI FILIPPO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>263</v>
+        <v>0</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>11</v>
+        <v>209</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>152</v>
+        <v>237</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03610</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MONTEBELLUNA</t>
+          <t>PIANIGA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA BASSANESE, 58</t>
+          <t>STAZIONE 1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,56 +1723,56 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>57</v>
+        <v>170</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>04247</t>
+          <t>56062</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>BRUGNERA</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>UNGARESCA 0017</t>
+          <t>VIALE TRICESIMO 93</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,35 +1782,35 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>FELICI FILIPPO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>91</v>
+        <v>286</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>56062</t>
+          <t>04247</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>BRUGNERA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIALE TRICESIMO 93</t>
+          <t>UNGARESCA 0017</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,35 +1841,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>285</v>
+        <v>95</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>8</v>
@@ -1916,7 +1916,7 @@
         <v>3</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>18</v>
@@ -1925,14 +1925,14 @@
         <v>8</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>5</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>80</v>
@@ -1975,7 +1975,7 @@
         <v>2</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>7</v>
@@ -1984,7 +1984,7 @@
         <v>14</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>1</v>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O33" headerRowCount="1">
-  <autoFilter ref="A10:O33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O35" headerRowCount="1">
+  <autoFilter ref="A10:O35"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,14 +521,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3327</v>
+        <v>3686</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2196</v>
+        <v>2463</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1652</v>
+        <v>1816</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>GERBO ANDREA</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>59131</t>
+          <t>03269</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BELLUNO</t>
+          <t>ESTE</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO</t>
+          <t>BORGO FURO 12</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,56 +1015,56 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>315</v>
+        <v>460</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>362</v>
+        <v>394</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>59131</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>MOGLIANO VENETO</t>
+          <t>BELLUNO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA CASALE SUL SILE 14</t>
+          <t>VIA VITTORIO VENETO</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,35 +1074,35 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>GERBO ANDREA</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>229</v>
+        <v>274</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>186</v>
+        <v>315</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>470</v>
+        <v>20</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>156</v>
+        <v>231</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>308</v>
+        <v>362</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>PORDENONE</t>
+          <t>MOGLIANO VENETO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIALE VENEZIA 46</t>
+          <t>VIA CASALE SUL SILE 14</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,56 +1133,56 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>434</v>
+        <v>186</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>201</v>
+        <v>470</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>364</v>
+        <v>96</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>336</v>
+        <v>308</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>03733</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>VENEZIA</t>
+          <t>PORDENONE</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ROTATORIA ROMEA</t>
+          <t>VIALE VENEZIA 46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,56 +1192,56 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>MARINI EMANUELE</t>
+          <t>FELICI FILIPPO</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>154</v>
+        <v>434</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>18</v>
+        <v>201</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>20</v>
+        <v>364</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>397</v>
+        <v>336</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04044</t>
+          <t>03733</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>TRIESTE</t>
+          <t>VENEZIA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>V.LE MIRAMARE  49 0049</t>
+          <t>ROTATORIA ROMEA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,35 +1251,35 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>ZAMPIERI ANTONIO</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>22</v>
+        <v>154</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>240</v>
+        <v>18</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>264</v>
+        <v>397</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>03743</t>
+          <t>04044</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>VENEZIA</t>
+          <t>TRIESTE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA ORLANDA 6A</t>
+          <t>V.LE MIRAMARE  49 0049</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>MARINI EMANUELE</t>
+          <t>ZAMPIERI ANTONIO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>10</v>
+        <v>240</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>95</v>
+        <v>141</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>157</v>
+        <v>264</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>51141</t>
+          <t>03743</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SPINEA</t>
+          <t>VENEZIA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COSTITUZIONE CREA</t>
+          <t>VIA ORLANDA 6A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>27</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>222</v>
+        <v>157</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>56033</t>
+          <t>51141</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CASTELFRANCO VENETO</t>
+          <t>SPINEA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA CIRCONVALLAZIONE EST 85</t>
+          <t>COSTITUZIONE CREA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>224</v>
+        <v>118</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>03734</t>
+          <t>56033</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MUSILE DI PIAVE</t>
+          <t>CASTELFRANCO VENETO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIALE MARCONI 48</t>
+          <t>VIA CIRCONVALLAZIONE EST 85</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,32 +1487,32 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>MARINI EMANUELE</t>
+          <t>GERBO ANDREA</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>158</v>
+        <v>224</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>37</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>03734</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>PORTOGRUARO</t>
+          <t>MUSILE DI PIAVE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA PORDENONE, 78</t>
+          <t>VIALE MARCONI 48</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>275</v>
+        <v>158</v>
       </c>
       <c r="H23" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="I23" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>246</v>
-      </c>
       <c r="J23" s="12" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>03610</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MONTEBELLUNA</t>
+          <t>PORTOGRUARO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA BASSANESE, 58</t>
+          <t>VIA PORDENONE, 78</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,56 +1605,56 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>52834</t>
+          <t>03610</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>MONTEBELLUNA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIALE MONSIGNORE GIUSEPPE NOGARA 92</t>
+          <t>VIA BASSANESE, 58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>GERBO ANDREA</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
@@ -1674,25 +1674,25 @@
         <v>0</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>209</v>
+        <v>26</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>237</v>
+        <v>61</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>52834</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>PIANIGA</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>STAZIONE 1</t>
+          <t>VIALE MONSIGNORE GIUSEPPE NOGARA 92</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,56 +1723,56 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>FELICI FILIPPO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>9</v>
+        <v>209</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="K26" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>237</v>
+      </c>
+      <c r="N26" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L26" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="M26" s="12" t="n">
-        <v>170</v>
-      </c>
-      <c r="N26" s="12" t="n">
-        <v>48</v>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>56062</t>
+          <t>13227</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>SOLESINO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIALE TRICESIMO 93</t>
+          <t>VIA IV NOVEMBRE 145</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>286</v>
+        <v>2</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>04247</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BRUGNERA</t>
+          <t>PIANIGA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>UNGARESCA 0017</t>
+          <t>STAZIONE 1</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I28" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="K28" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="J28" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="L28" s="12" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>04131</t>
+          <t>56062</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MONFALCONE</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA VALENTINIS, SS 14 61</t>
+          <t>VIALE TRICESIMO 93</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,56 +1900,56 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>ZAMPIERI ANTONIO</t>
+          <t>FELICI FILIPPO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>44</v>
+        <v>286</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>03679</t>
+          <t>04247</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SAN DONÀ DI PIAVE</t>
+          <t>BRUGNERA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIA NOVENTA 150</t>
+          <t>UNGARESCA 0017</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,35 +1959,35 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>MARINI EMANUELE</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>13623</t>
+          <t>04131</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>VITTORIO VENETO</t>
+          <t>MONFALCONE</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA S.ANTONIO DA PADOVA SS 51</t>
+          <t>VIA VALENTINIS, SS 14 61</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,35 +2018,35 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>ZAMPIERI ANTONIO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>14289</t>
+          <t>03679</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SAN DANIELE DEL FRIULI</t>
+          <t>SAN DONÀ DI PIAVE</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA VENEZIA, 89/91</t>
+          <t>VIA NOVENTA 150</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,92 +2077,210 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M32" s="12" t="n">
+        <v>117</v>
+      </c>
+      <c r="N32" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>13623</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>VITTORIO VENETO</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>VIA S.ANTONIO DA PADOVA SS 51</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>GERBO ANDREA</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="N33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>14289</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SAN DANIELE DEL FRIULI</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>VIA VENEZIA, 89/91</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>FELICI FILIPPO</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K34" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>04051</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>TRIESTE</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>ALFONSO VALERIO 0001</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr"/>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>ZAMPIERI ANTONIO</t>
         </is>
       </c>
-      <c r="F33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="12" t="n">
+      <c r="F35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="H33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
+      <c r="H35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAIOLINI OMAR.xlsx
@@ -684,13 +684,13 @@
         <v>25</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3686</v>
+        <v>3684</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2463</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1816</v>
+        <v>1795</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>998</v>
+        <v>960</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>167</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>348</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>120</v>
@@ -863,7 +863,7 @@
         <v>290</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>965</v>
+        <v>952</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>71</v>
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>548</v>
@@ -913,7 +913,7 @@
         <v>9</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>54</v>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>67</v>
@@ -981,14 +981,14 @@
         <v>103</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>91</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>111</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>87</v>
@@ -1040,7 +1040,7 @@
         <v>84</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>8</v>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>20</v>
@@ -1090,7 +1090,7 @@
         <v>13</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>80</v>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>186</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>96</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>42</v>
@@ -1158,7 +1158,7 @@
         <v>75</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>9</v>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>46</v>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>18</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>24</v>
@@ -1276,7 +1276,7 @@
         <v>72</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>13</v>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>22</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>62</v>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>49</v>
@@ -1385,7 +1385,7 @@
         <v>5</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>27</v>
@@ -1394,14 +1394,14 @@
         <v>28</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>3</v>
@@ -1444,7 +1444,7 @@
         <v>10</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>27</v>
@@ -1453,7 +1453,7 @@
         <v>56</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>4</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>224</v>
@@ -1503,7 +1503,7 @@
         <v>31</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>6</v>
@@ -1512,7 +1512,7 @@
         <v>37</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
@@ -1553,16 +1553,16 @@
         <v>89</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>11</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>13</v>
@@ -1571,7 +1571,7 @@
         <v>37</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>13227</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PORTOGRUARO</t>
+          <t>SOLESINO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA PORDENONE, 78</t>
+          <t>VIA IV NOVEMBRE 145</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1612,49 +1612,49 @@
         <v>66</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>275</v>
+        <v>2</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="L24" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M24" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="N24" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="M24" s="12" t="n">
-        <v>157</v>
-      </c>
-      <c r="N24" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>03610</t>
+          <t>52834</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>MONTEBELLUNA</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA BASSANESE, 58</t>
+          <t>VIALE MONSIGNORE GIUSEPPE NOGARA 92</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,56 +1664,56 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>GERBO ANDREA</t>
+          <t>FELICI FILIPPO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>26</v>
+        <v>200</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>61</v>
+        <v>230</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>52834</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>PORTOGRUARO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIALE MONSIGNORE GIUSEPPE NOGARA 92</t>
+          <t>VIA PORDENONE, 78</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,56 +1723,56 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>FELICI FILIPPO</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>209</v>
+        <v>11</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SOLESINO</t>
+          <t>PIANIGA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA IV NOVEMBRE 145</t>
+          <t>STAZIONE 1</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>MARINI EMANUELE</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
         <v>64</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>79</v>
+        <v>170</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>03610</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>PIANIGA</t>
+          <t>MONTEBELLUNA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>STAZIONE 1</t>
+          <t>VIA BASSANESE, 58</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,39 +1841,39 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>GERBO ANDREA</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>170</v>
+        <v>61</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
         <v>11</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>21</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>95</v>
@@ -1975,7 +1975,7 @@
         <v>5</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>13</v>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>44</v>
@@ -2034,7 +2034,7 @@
         <v>3</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>18</v>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>80</v>
@@ -2093,7 +2093,7 @@
         <v>2</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>7</v>
@@ -2146,13 +2146,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>4</v>
@@ -2211,7 +2211,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>5</v>
